--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104602_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104602_W16.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5953</v>
+        <v>5.9996</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2788</v>
+        <v>3.4308</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3166</v>
+        <v>2.5688</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7437</v>
+        <v>1.7235</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8082</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9355</v>
+        <v>0.9246</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3486</v>
+        <v>1.3002</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0559</v>
+        <v>-0.0764</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4045</v>
+        <v>1.3767</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3952</v>
+        <v>0.4233</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8641</v>
+        <v>0.8754</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.469</v>
+        <v>-0.4521</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3771</v>
+        <v>0.0501</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0302</v>
+        <v>0.1808</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3469</v>
+        <v>-0.1308</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2519</v>
+        <v>5.9465</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6889</v>
+        <v>4.5512</v>
       </c>
       <c r="F3" t="n">
-        <v>1.563</v>
+        <v>1.3953</v>
       </c>
       <c r="G3" t="n">
-        <v>4.236</v>
+        <v>4.2251</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3032</v>
+        <v>-0.2935</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5392</v>
+        <v>4.5186</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0087</v>
+        <v>3.9799</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6565</v>
+        <v>4.6316</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2274</v>
+        <v>0.2452</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2782</v>
+        <v>0.62</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2014</v>
+        <v>0.0119</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0475</v>
+        <v>4.6592</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2977</v>
+        <v>4.2687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7498</v>
+        <v>0.3905</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0659</v>
+        <v>5.1206</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6737</v>
+        <v>4.182</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6078</v>
+        <v>0.9386</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4106</v>
+        <v>4.8409</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1949</v>
+        <v>3.2922</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2158</v>
+        <v>1.5486</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3447</v>
+        <v>0.2798</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5212</v>
+        <v>0.8898</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8236</v>
+        <v>-0.61</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6867</v>
+        <v>-0.1914</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4729</v>
+        <v>0.2018</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2138</v>
+        <v>-0.3932</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2534</v>
+        <v>-1.8634</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4141</v>
+        <v>-0.7739</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5492</v>
+        <v>4.1741</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3462</v>
+        <v>3.6073</v>
       </c>
       <c r="F5" t="n">
-        <v>0.203</v>
+        <v>0.5668</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1232</v>
+        <v>0.0733</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1875</v>
+        <v>0.6858</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9356</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8694</v>
+        <v>1.3898</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3075</v>
+        <v>1.1893</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5619</v>
+        <v>0.2004</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2538</v>
+        <v>-1.3164</v>
       </c>
       <c r="N5" t="n">
-        <v>0.88</v>
+        <v>-0.5036</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6263</v>
+        <v>-0.8129</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2979</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.248</v>
+        <v>0.8126</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.0077</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8639</v>
+        <v>1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7712</v>
+        <v>1.405</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.16</v>
+        <v>2.7556</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9729</v>
+        <v>3.5672</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1871</v>
+        <v>-0.8115</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4048</v>
+        <v>1.5474</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8369</v>
+        <v>2.7314</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5679</v>
+        <v>-1.1839</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2814</v>
+        <v>2.9496</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4604</v>
+        <v>2.6889</v>
       </c>
       <c r="L6" t="n">
-        <v>0.821</v>
+        <v>0.2607</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1233</v>
+        <v>-1.4022</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3764</v>
+        <v>0.0424</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2531</v>
+        <v>-1.4446</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1674</v>
+        <v>0.6132</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8257</v>
+        <v>0.6176</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3417</v>
+        <v>-0.0044</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5463</v>
+        <v>-0.3155</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9444</v>
+        <v>2.7309</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9093</v>
+        <v>1.2227</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9649</v>
+        <v>1.5082</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5401</v>
+        <v>5.6956</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7315</v>
+        <v>1.809</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1914</v>
+        <v>3.8867</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9626</v>
+        <v>4.6303</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7014</v>
+        <v>1.4651</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2612</v>
+        <v>3.1651</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4225</v>
+        <v>1.0653</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0301</v>
+        <v>0.3438</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4526</v>
+        <v>0.7215</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8184</v>
+        <v>-0.4607</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9467</v>
+        <v>0.0556</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1282</v>
+        <v>-0.5163</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8295</v>
+        <v>2.2994</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5738</v>
+        <v>0.3923</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2557</v>
+        <v>1.9071</v>
       </c>
       <c r="G8" t="n">
-        <v>5.6817</v>
+        <v>1.4201</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8007</v>
+        <v>0.8386</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8811</v>
+        <v>0.5816</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6438</v>
+        <v>1.2706</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4719</v>
+        <v>0.4514</v>
       </c>
       <c r="L8" t="n">
-        <v>3.1719</v>
+        <v>0.8192</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0379</v>
+        <v>0.1495</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3288</v>
+        <v>0.3871</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7091</v>
+        <v>-0.2377</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3571</v>
+        <v>0.2859</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>0.2598</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.731</v>
+        <v>0.0261</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7172</v>
+        <v>-1.5385</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4186</v>
+        <v>-1.3102</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2986</v>
+        <v>-0.2282</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8648</v>
+        <v>-1.8682</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7287</v>
+        <v>0.7267</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5936</v>
+        <v>-2.595</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0013</v>
+        <v>-1.0105</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5329</v>
+        <v>-0.3531</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8424</v>
+        <v>-3.4019</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.992</v>
+        <v>-0.3607</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8504</v>
+        <v>-3.0412</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3723</v>
+        <v>-1.375</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4633</v>
+        <v>-0.457</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.909</v>
+        <v>-0.918</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5379</v>
+        <v>0.5154</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7009</v>
+        <v>0.6845</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9103</v>
+        <v>-1.8904</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2187</v>
+        <v>0.2219</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>0.1043</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3378</v>
+        <v>0.1176</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0781</v>
+        <v>-3.5478</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2162</v>
+        <v>-3.814</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1382</v>
+        <v>0.2662</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9037</v>
+        <v>-4.9101</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9148</v>
+        <v>1.9156</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.8185</v>
+        <v>-6.8257</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7321</v>
+        <v>-2.766</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0261</v>
+        <v>2.0167</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.7582</v>
+        <v>-4.7828</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1716</v>
+        <v>-2.1441</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0603</v>
+        <v>-2.043</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0402</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3085</v>
+        <v>0.1389</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2683</v>
+        <v>0.3616</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.481</v>
+        <v>-4.4273</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7715</v>
+        <v>-3.7859</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7096</v>
+        <v>-0.6414</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1799</v>
+        <v>-3.1846</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8023</v>
+        <v>-0.8041</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3777</v>
+        <v>-2.3805</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8209</v>
+        <v>-0.8157</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1669</v>
+        <v>-0.1046</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1113</v>
+        <v>0.1743</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.2591</v>
+        <v>15.6498</v>
       </c>
       <c r="E13" t="n">
-        <v>10.6693</v>
+        <v>11.7694</v>
       </c>
       <c r="F13" t="n">
-        <v>3.589899999999999</v>
+        <v>3.8806</v>
       </c>
       <c r="G13" t="n">
-        <v>8.474699999999999</v>
+        <v>8.467700000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>12.1132</v>
+        <v>12.1334</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.6387</v>
+        <v>-3.6654</v>
       </c>
       <c r="J13" t="n">
-        <v>14.9705</v>
+        <v>14.7313</v>
       </c>
       <c r="K13" t="n">
-        <v>10.0806</v>
+        <v>9.9856</v>
       </c>
       <c r="L13" t="n">
-        <v>4.890099999999999</v>
+        <v>4.7454</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.496</v>
+        <v>-6.2635</v>
       </c>
       <c r="N13" t="n">
-        <v>2.0326</v>
+        <v>2.147699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.528799999999999</v>
+        <v>-8.411200000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>4.536600000000001</v>
+        <v>4.552700000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3418</v>
+        <v>-11.3817</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8782</v>
+        <v>15.9342</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6049</v>
+        <v>1.9987</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9982</v>
+        <v>2.4128</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3932</v>
+        <v>-0.4143</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6429999999999996</v>
+        <v>0.6311000000000002</v>
       </c>
       <c r="W13" t="n">
-        <v>6.0421</v>
+        <v>6.0071</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.3991</v>
+        <v>-5.3759</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7504</v>
+        <v>2.8089</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5315</v>
+        <v>0.8752</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2189</v>
+        <v>1.9337</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4836</v>
+        <v>1.4939</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6969</v>
+        <v>-0.6979</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1805</v>
+        <v>2.1917</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1575</v>
+        <v>1.1472</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3739</v>
+        <v>0.3652</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M14" t="n">
-        <v>0.326</v>
+        <v>0.3467</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0665</v>
+        <v>0.107</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6926</v>
+        <v>0.379</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4627</v>
+        <v>2.3099</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4902</v>
+        <v>3.1549</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0275</v>
+        <v>-0.845</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4232</v>
+        <v>3.4167</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9496</v>
+        <v>0.9424</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4736</v>
+        <v>2.4743</v>
       </c>
       <c r="J15" t="n">
-        <v>5.5652</v>
+        <v>5.536</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2094</v>
+        <v>2.1923</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3558</v>
+        <v>3.3436</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.142</v>
+        <v>-2.1193</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0.3077</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7652</v>
+        <v>-0.0561</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2072</v>
+        <v>0.3637</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8174</v>
+        <v>0.2207</v>
       </c>
       <c r="E16" t="n">
-        <v>1.957</v>
+        <v>1.5905</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1396</v>
+        <v>-1.3698</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3466</v>
+        <v>0.3511</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0534</v>
+        <v>0.0545</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2932</v>
+        <v>0.2966</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7056</v>
+        <v>1.6955</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.359</v>
+        <v>-1.3444</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4954</v>
+        <v>-0.1092</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0907</v>
+        <v>-0.2627</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4047</v>
+        <v>0.1535</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2897</v>
+        <v>-0.1612</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9562</v>
+        <v>-0.0639</v>
       </c>
       <c r="F17" t="n">
-        <v>1.246</v>
+        <v>-0.0973</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3769</v>
+        <v>0.819</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0433</v>
+        <v>-0.6718</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6664</v>
+        <v>1.4908</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1215</v>
+        <v>1.646</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.492</v>
+        <v>0.0755</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3705</v>
+        <v>1.5705</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2554</v>
+        <v>-0.827</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5513</v>
+        <v>-0.7472</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2959</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8934</v>
+        <v>-0.9315</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2994</v>
+        <v>-0.2954</v>
       </c>
       <c r="U17" t="n">
-        <v>0.594</v>
+        <v>-0.6361</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2462</v>
+        <v>-0.1855</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4806</v>
+        <v>-1.3237</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2343</v>
+        <v>1.1382</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3228</v>
+        <v>-0.3737</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9683</v>
+        <v>-1.0426</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3545</v>
+        <v>0.669</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6625</v>
+        <v>-0.1319</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0866</v>
+        <v>-0.4966</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.749</v>
+        <v>0.3647</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6603</v>
+        <v>-0.2417</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0549</v>
+        <v>-0.546</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3946</v>
+        <v>0.3043</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3695</v>
+        <v>0.4158</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1553</v>
+        <v>-0.0536</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2141</v>
+        <v>0.4694</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4035</v>
+        <v>-0.2076</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7935</v>
+        <v>0.6439</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.197</v>
+        <v>-0.8516</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8532</v>
+        <v>0.8573</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1673</v>
+        <v>-1.1689</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0205</v>
+        <v>2.0261</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0921</v>
+        <v>1.067</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4873</v>
+        <v>1.4741</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2389</v>
+        <v>-0.2097</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5333</v>
+        <v>0.552</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0298</v>
+        <v>-0.8373</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0302</v>
+        <v>-0.1467</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9996</v>
+        <v>-0.6906</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.136</v>
+        <v>-0.8797</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6051</v>
+        <v>-1.1962</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5309</v>
+        <v>0.3165</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8314</v>
+        <v>-1.3092</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6666</v>
+        <v>-0.9625</v>
       </c>
       <c r="I20" t="n">
-        <v>1.498</v>
+        <v>-0.3467</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6835</v>
+        <v>-0.6662</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0897</v>
+        <v>0.0862</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5938</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8521</v>
+        <v>-0.643</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7563</v>
+        <v>-1.0487</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0958</v>
+        <v>0.4057</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.926</v>
+        <v>0.727</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8861</v>
+        <v>0.4504</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0398</v>
+        <v>0.2766</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1269</v>
+        <v>-1.8802</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.042</v>
+        <v>-0.9355</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.085</v>
+        <v>-0.9447</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0561</v>
+        <v>-2.0542</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0215</v>
+        <v>-2.0246</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0346</v>
+        <v>-0.0296</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2949</v>
+        <v>-0.3057</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9666</v>
+        <v>-0.976</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7612</v>
+        <v>-1.7485</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0549</v>
+        <v>-1.0487</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3829</v>
+        <v>0.6293</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3871</v>
+        <v>0.5084</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0042</v>
+        <v>0.1209</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6838</v>
+        <v>-2.0677</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0372</v>
+        <v>0.2988</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6466</v>
+        <v>-2.3665</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1114</v>
+        <v>1.12</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0101</v>
+        <v>1.0109</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1014</v>
+        <v>0.1091</v>
       </c>
       <c r="J22" t="n">
-        <v>2.089</v>
+        <v>2.076</v>
       </c>
       <c r="K22" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L22" t="n">
-        <v>0.669</v>
+        <v>0.6626</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9776</v>
+        <v>-0.956</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7006</v>
+        <v>-1.0998</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7652</v>
+        <v>-0.4114</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9355</v>
+        <v>-0.6884</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0463</v>
+        <v>-3.5101</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8741</v>
+        <v>-1.8566</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1722</v>
+        <v>-1.6535</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.9181</v>
+        <v>-4.5859</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1917</v>
+        <v>-3.501</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.7264</v>
+        <v>-1.0849</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5175</v>
+        <v>-1.8493</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4196</v>
+        <v>-2.2655</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0979</v>
+        <v>0.4162</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4007</v>
+        <v>-2.7365</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7721</v>
+        <v>-1.2355</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6285</v>
+        <v>-1.5011</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.722</v>
+        <v>1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>1.4085</v>
+        <v>0.4109</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4729</v>
+        <v>-0.0073</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0644</v>
+        <v>0.4182</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1853</v>
+        <v>-0.4733</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3856</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3472</v>
+        <v>-4.9514</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7139</v>
+        <v>-3.7446</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6333</v>
+        <v>-1.2068</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2767</v>
+        <v>-4.9224</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.8715</v>
+        <v>-1.2001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4052</v>
+        <v>-3.7224</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3823</v>
+        <v>-2.5467</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2725</v>
+        <v>-0.4384</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8902</v>
+        <v>-2.1083</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8944</v>
+        <v>-2.3758</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.599</v>
+        <v>-0.7617</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2954</v>
+        <v>-1.6141</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6611</v>
+        <v>0.5236</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8953</v>
+        <v>0.6522</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2341</v>
+        <v>-0.1286</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5892</v>
+        <v>-4.9624</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6529</v>
+        <v>-1.3235</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9363</v>
+        <v>-3.6389</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.5734</v>
+        <v>-3.2803</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.4991</v>
+        <v>-2.872</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0743</v>
+        <v>-0.4083</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.8182</v>
+        <v>-1.4044</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2552</v>
+        <v>-2.2827</v>
       </c>
       <c r="L25" t="n">
-        <v>0.437</v>
+        <v>0.8783</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.7552</v>
+        <v>-1.8759</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.244</v>
+        <v>-0.5893</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5113</v>
+        <v>-1.2866</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6677999999999999</v>
+        <v>0.0417</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8347</v>
+        <v>0.3085</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1669</v>
+        <v>-0.2669</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.4822</v>
+        <v>-2.1789</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.4822</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.2589</v>
+        <v>-13.4663</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.589799999999999</v>
+        <v>-3.8807</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.6692</v>
+        <v>-9.585699999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.474600000000001</v>
+        <v>-8.467699999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.1131</v>
+        <v>-12.1336</v>
       </c>
       <c r="I26" t="n">
-        <v>3.6386</v>
+        <v>3.6657</v>
       </c>
       <c r="J26" t="n">
-        <v>6.496</v>
+        <v>6.263500000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.0327</v>
+        <v>-2.1477</v>
       </c>
       <c r="L26" t="n">
-        <v>8.5289</v>
+        <v>8.411</v>
       </c>
       <c r="M26" t="n">
-        <v>-14.9708</v>
+        <v>-14.7311</v>
       </c>
       <c r="N26" t="n">
-        <v>-10.0806</v>
+        <v>-9.985799999999998</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.8901</v>
+        <v>-4.7454</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.5367</v>
+        <v>-4.552599999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8784</v>
+        <v>-15.9343</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6048999999999998</v>
+        <v>0.1851999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3932000000000002</v>
+        <v>0.4142999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9981000000000002</v>
+        <v>-0.2293</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6428999999999998</v>
+        <v>-0.6310000000000002</v>
       </c>
       <c r="W26" t="n">
-        <v>5.3992</v>
+        <v>5.376099999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.042099999999999</v>
+        <v>-6.007</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104602_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104602_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.3759</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104602_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.007</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
